--- a/public/import-templates/customers_import_template.xlsx
+++ b/public/import-templates/customers_import_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project_Web\Final_Year_Btech_2026\Prototype\multipos_prototype_v0.1\public\import-templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project_Web\Final_Year_Btech_2026\Prototype\Back-Up-Mulitpos\multipos_prototype_v0.1_back_up\public\import-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A560868-1047-456E-B1E9-F745B3E10361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A68153-1DB7-404A-B97F-C5455C2B16E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C83875D7-564F-4117-A0A5-4E51A0F7749F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="128">
   <si>
     <t>firstName</t>
   </si>
@@ -120,23 +120,314 @@
     <t>Takoradi-Ghana</t>
   </si>
   <si>
+    <t>Akosua</t>
+  </si>
+  <si>
+    <t>Owusu</t>
+  </si>
+  <si>
+    <t>akosua.owusu@example.com</t>
+  </si>
+  <si>
+    <t>Cape Coast-Ghana</t>
+  </si>
+  <si>
+    <t>Yaw</t>
+  </si>
+  <si>
+    <t>Adjei</t>
+  </si>
+  <si>
+    <t>yaw.adjei@example.com</t>
+  </si>
+  <si>
+    <t>Tema-Ghana</t>
+  </si>
+  <si>
+    <t>Abena</t>
+  </si>
+  <si>
+    <t>Frimpong</t>
+  </si>
+  <si>
+    <t>abena.frimpong@example.com</t>
+  </si>
+  <si>
+    <t>Ho-Ghana</t>
+  </si>
+  <si>
+    <t>Kojo</t>
+  </si>
+  <si>
+    <t>Appiah</t>
+  </si>
+  <si>
+    <t>kojo.appiah@example.com</t>
+  </si>
+  <si>
+    <t>Sunyani-Ghana</t>
+  </si>
+  <si>
+    <t>Efua</t>
+  </si>
+  <si>
+    <t>Antwi</t>
+  </si>
+  <si>
+    <t>efua.antwi@example.com</t>
+  </si>
+  <si>
+    <t>Tamale-Ghana</t>
+  </si>
+  <si>
+    <t>Kwabena</t>
+  </si>
+  <si>
+    <t>Sarpong</t>
+  </si>
+  <si>
+    <t>kwabena.sarpong@example.com</t>
+  </si>
+  <si>
+    <t>Koforidua-Ghana</t>
+  </si>
+  <si>
+    <t>Maa</t>
+  </si>
+  <si>
+    <t>Agyeman</t>
+  </si>
+  <si>
+    <t>maa.agyeman@example.com</t>
+  </si>
+  <si>
+    <t>Bolgatanga-Ghana</t>
+  </si>
+  <si>
+    <t>Nana</t>
+  </si>
+  <si>
+    <t>Osei</t>
+  </si>
+  <si>
+    <t>nana.osei@example.com</t>
+  </si>
+  <si>
+    <t>Adwoa</t>
+  </si>
+  <si>
+    <t>Kwarteng</t>
+  </si>
+  <si>
+    <t>adwoa.kwarteng@example.com</t>
+  </si>
+  <si>
+    <t>Baah</t>
+  </si>
+  <si>
+    <t>yaw.baah@example.com</t>
+  </si>
+  <si>
+    <t>Akua</t>
+  </si>
+  <si>
+    <t>Darko</t>
+  </si>
+  <si>
+    <t>akua.darko@example.com</t>
+  </si>
+  <si>
+    <t>Arthur</t>
+  </si>
+  <si>
+    <t>kojo.arthur@example.com</t>
+  </si>
+  <si>
+    <t>Bonsu</t>
+  </si>
+  <si>
+    <t>efua.bonsu@example.com</t>
+  </si>
+  <si>
+    <t>Tetteh</t>
+  </si>
+  <si>
+    <t>kwame.tetteh@example.com</t>
+  </si>
+  <si>
+    <t>Yeboah</t>
+  </si>
+  <si>
+    <t>ama.yeboah@example.com</t>
+  </si>
+  <si>
+    <t>Gyasi</t>
+  </si>
+  <si>
+    <t>kofi.gyasi@example.com</t>
+  </si>
+  <si>
+    <t>Nyarko</t>
+  </si>
+  <si>
+    <t>akosua.nyarko@example.com</t>
+  </si>
+  <si>
+    <t>Opoku</t>
+  </si>
+  <si>
+    <t>yaw.opoku@example.com</t>
+  </si>
+  <si>
+    <t>Ofori</t>
+  </si>
+  <si>
+    <t>abena.ofori@example.com</t>
+  </si>
+  <si>
+    <t>Amankwah</t>
+  </si>
+  <si>
+    <t>kojo.amankwah@example.com</t>
+  </si>
+  <si>
+    <t>Addo</t>
+  </si>
+  <si>
+    <t>efua.addo@example.com</t>
+  </si>
+  <si>
+    <t>Aidoo</t>
+  </si>
+  <si>
+    <t>kwabena.aidoo@example.com</t>
+  </si>
+  <si>
+    <t>Sam</t>
+  </si>
+  <si>
+    <t>maa.sam@example.com</t>
+  </si>
+  <si>
+    <t>nana.boateng@example.com</t>
+  </si>
+  <si>
+    <t>Kusi</t>
+  </si>
+  <si>
+    <t>adwoa.kusi@example.com</t>
+  </si>
+  <si>
+    <t>Asiedu</t>
+  </si>
+  <si>
+    <t>yaw.asiedu@example.com</t>
+  </si>
+  <si>
+    <t>Mintah</t>
+  </si>
+  <si>
+    <t>akua.mintah@example.com</t>
+  </si>
+  <si>
     <t>0240000000</t>
   </si>
   <si>
-    <t>0240000001</t>
-  </si>
-  <si>
-    <t>0240000002</t>
-  </si>
-  <si>
-    <t>0240000003</t>
+    <t>0241000001</t>
+  </si>
+  <si>
+    <t>0241000002</t>
+  </si>
+  <si>
+    <t>0241000003</t>
+  </si>
+  <si>
+    <t>0241000004</t>
+  </si>
+  <si>
+    <t>0241000005</t>
+  </si>
+  <si>
+    <t>0241000006</t>
+  </si>
+  <si>
+    <t>0241000007</t>
+  </si>
+  <si>
+    <t>0241000008</t>
+  </si>
+  <si>
+    <t>0241000009</t>
+  </si>
+  <si>
+    <t>0241000010</t>
+  </si>
+  <si>
+    <t>0241000011</t>
+  </si>
+  <si>
+    <t>0241000012</t>
+  </si>
+  <si>
+    <t>0241000013</t>
+  </si>
+  <si>
+    <t>0241000014</t>
+  </si>
+  <si>
+    <t>0241000015</t>
+  </si>
+  <si>
+    <t>0241000016</t>
+  </si>
+  <si>
+    <t>0241000017</t>
+  </si>
+  <si>
+    <t>0241000018</t>
+  </si>
+  <si>
+    <t>0241000019</t>
+  </si>
+  <si>
+    <t>0241000020</t>
+  </si>
+  <si>
+    <t>0241000021</t>
+  </si>
+  <si>
+    <t>0241000022</t>
+  </si>
+  <si>
+    <t>0241000023</t>
+  </si>
+  <si>
+    <t>0241000024</t>
+  </si>
+  <si>
+    <t>0241000025</t>
+  </si>
+  <si>
+    <t>0241000026</t>
+  </si>
+  <si>
+    <t>0241000027</t>
+  </si>
+  <si>
+    <t>0241000028</t>
+  </si>
+  <si>
+    <t>0241000029</t>
+  </si>
+  <si>
+    <t>0241000030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,12 +439,6 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -189,8 +474,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,15 +810,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1A82FA9-61CC-4CDD-B48C-4ECBD92830DE}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.36328125" bestFit="1" customWidth="1"/>
@@ -557,7 +842,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -592,8 +877,8 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>27</v>
+      <c r="D2" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -604,7 +889,7 @@
       <c r="G2" s="2">
         <v>44927</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
         <v>45413</v>
       </c>
       <c r="I2">
@@ -627,8 +912,8 @@
       <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>28</v>
+      <c r="D3" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -636,10 +921,10 @@
       <c r="F3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3">
         <v>44928</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3">
         <v>45444</v>
       </c>
       <c r="I3">
@@ -662,8 +947,8 @@
       <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>29</v>
+      <c r="D4" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
@@ -671,10 +956,10 @@
       <c r="F4" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4">
         <v>44960</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4">
         <v>45432</v>
       </c>
       <c r="I4">
@@ -697,8 +982,8 @@
       <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>30</v>
+      <c r="D5" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
@@ -706,10 +991,10 @@
       <c r="F5" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5">
         <v>44990</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5">
         <v>45400</v>
       </c>
       <c r="I5">
@@ -722,8 +1007,952 @@
         <v>3000</v>
       </c>
     </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>45026</v>
+      </c>
+      <c r="H6">
+        <v>45453</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>45058</v>
+      </c>
+      <c r="H7">
+        <v>45474</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>45091</v>
+      </c>
+      <c r="H8">
+        <v>45488</v>
+      </c>
+      <c r="I8">
+        <v>9</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>45127</v>
+      </c>
+      <c r="H9">
+        <v>45473</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>45163</v>
+      </c>
+      <c r="H10">
+        <v>45434</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>45170</v>
+      </c>
+      <c r="H11">
+        <v>45448</v>
+      </c>
+      <c r="I11">
+        <v>11</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>45204</v>
+      </c>
+      <c r="H12">
+        <v>45475</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>45241</v>
+      </c>
+      <c r="H13">
+        <v>45455</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>45275</v>
+      </c>
+      <c r="H14">
+        <v>45481</v>
+      </c>
+      <c r="I14">
+        <v>6</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>45311</v>
+      </c>
+      <c r="H15">
+        <v>45493</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>45324</v>
+      </c>
+      <c r="H16">
+        <v>45461</v>
+      </c>
+      <c r="I16">
+        <v>7</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>45354</v>
+      </c>
+      <c r="H17">
+        <v>45483</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>45386</v>
+      </c>
+      <c r="H18">
+        <v>45498</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>45417</v>
+      </c>
+      <c r="H19">
+        <v>45501</v>
+      </c>
+      <c r="I19">
+        <v>6</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>45449</v>
+      </c>
+      <c r="H20">
+        <v>45503</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>45480</v>
+      </c>
+      <c r="H21">
+        <v>45504</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22">
+        <v>45512</v>
+      </c>
+      <c r="H22">
+        <v>45505</v>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>45544</v>
+      </c>
+      <c r="H23">
+        <v>45506</v>
+      </c>
+      <c r="I23">
+        <v>6</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>45575</v>
+      </c>
+      <c r="H24">
+        <v>45507</v>
+      </c>
+      <c r="I24">
+        <v>8</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>45607</v>
+      </c>
+      <c r="H25">
+        <v>45508</v>
+      </c>
+      <c r="I25">
+        <v>9</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>45638</v>
+      </c>
+      <c r="H26">
+        <v>45509</v>
+      </c>
+      <c r="I26">
+        <v>7</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>45658</v>
+      </c>
+      <c r="H27">
+        <v>45510</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" t="s">
+        <v>5</v>
+      </c>
+      <c r="G28">
+        <v>45690</v>
+      </c>
+      <c r="H28">
+        <v>45511</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>45719</v>
+      </c>
+      <c r="H29">
+        <v>45512</v>
+      </c>
+      <c r="I29">
+        <v>4</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <v>45751</v>
+      </c>
+      <c r="H30">
+        <v>45513</v>
+      </c>
+      <c r="I30">
+        <v>6</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>45782</v>
+      </c>
+      <c r="H31">
+        <v>45514</v>
+      </c>
+      <c r="I31">
+        <v>5</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>45814</v>
+      </c>
+      <c r="H32">
+        <v>45515</v>
+      </c>
+      <c r="I32">
+        <v>7</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
